--- a/registro_certificados1.xlsx
+++ b/registro_certificados1.xlsx
@@ -550,12 +550,12 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260019.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260019.pdf</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -585,12 +585,12 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260020.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260020.pdf</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -620,12 +620,12 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260031.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260031.pdf</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260042.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260042.pdf</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260053.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260053.pdf</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -725,12 +725,12 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260064.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260064.pdf</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260075.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260075.pdf</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260086.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260086.pdf</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260097.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260097.pdf</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260109.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260109.pdf</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260110.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260110.pdf</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260121.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260121.pdf</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260132.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260132.pdf</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260143.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260143.pdf</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260154.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260154.pdf</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260165.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260165.pdf</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260176.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260176.pdf</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260187.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260187.pdf</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260198.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260198.pdf</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260200.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260200.pdf</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260211.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260211.pdf</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260222.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260222.pdf</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260233.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260233.pdf</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260244.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260244.pdf</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260255.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260255.pdf</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260266.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260266.pdf</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260277.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260277.pdf</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260288.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260288.pdf</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260299.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260299.pdf</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260301.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260301.pdf</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260312.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260312.pdf</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260323.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260323.pdf</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260334.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260334.pdf</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1705,12 +1705,12 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260345.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260345.pdf</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260356.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260356.pdf</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1775,12 +1775,12 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260367.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260367.pdf</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260378.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260378.pdf</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>https://IndoamericaCertificados/certificados/A260389.pdf</t>
+          <t>https://indoamericacertificados.github.io/certificados/A260389.pdf</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:21</t>
+          <t>12/06/2026 05:38</t>
         </is>
       </c>
     </row>

--- a/registro_certificados1.xlsx
+++ b/registro_certificados1.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 05:38</t>
+          <t>12/06/2026 16:44</t>
         </is>
       </c>
     </row>

--- a/registro_certificados1.xlsx
+++ b/registro_certificados1.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -530,12 +530,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Excelencia academica-B26-1</t>
+          <t>Certificados PONENTES - Conversatorio la niña y la mujer page-0001</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Excelencia academica-B26-1.png</t>
+          <t>Certificados PONENTES - Conversatorio la niña y la mujer_page-0001.png</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -565,12 +565,12 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Excelencia academica-B26-2</t>
+          <t>Certificados PONENTES - Conversatorio la niña y la mujer page-0002</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Excelencia academica-B26-2.png</t>
+          <t>Certificados PONENTES - Conversatorio la niña y la mujer_page-0002.png</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -600,12 +600,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Excelencia academica-B26-3</t>
+          <t>Certificados PONENTES - Conversatorio la niña y la mujer page-0003</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Excelencia academica-B26-3.png</t>
+          <t>Certificados PONENTES - Conversatorio la niña y la mujer_page-0003.png</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Excelencia academica-B26-4</t>
+          <t>Certificados PONENTES - Conversatorio la niña y la mujer page-0004</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Excelencia academica-B26-4.png</t>
+          <t>Certificados PONENTES - Conversatorio la niña y la mujer_page-0004.png</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -670,12 +670,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Excelencia academica-B26-5</t>
+          <t>Certificados PONENTES - Conversatorio la niña y la mujer page-0005</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Excelencia academica-B26-5.png</t>
+          <t>Certificados PONENTES - Conversatorio la niña y la mujer_page-0005.png</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Excelencia academica-B26-6</t>
+          <t>Certificados PONENTES - Conversatorio la niña y la mujer page-0006</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Excelencia academica-B26-6.png</t>
+          <t>Certificados PONENTES - Conversatorio la niña y la mujer_page-0006.png</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -740,12 +740,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Hackaton Final-1</t>
+          <t>Excelencia academica-B26-1</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Hackaton Final-1.png</t>
+          <t>Excelencia academica-B26-1.png</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Hackaton Final-10</t>
+          <t>Excelencia academica-B26-2</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Hackaton Final-10.png</t>
+          <t>Excelencia academica-B26-2.png</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Hackaton Final-11</t>
+          <t>Excelencia academica-B26-3</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Hackaton Final-11.png</t>
+          <t>Excelencia academica-B26-3.png</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Hackaton Final-12</t>
+          <t>Excelencia academica-B26-4</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Hackaton Final-12.png</t>
+          <t>Excelencia academica-B26-4.png</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Hackaton Final-2</t>
+          <t>Excelencia academica-B26-5</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Hackaton Final-2.png</t>
+          <t>Excelencia academica-B26-5.png</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Hackaton Final-3</t>
+          <t>Excelencia academica-B26-6</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Hackaton Final-3.png</t>
+          <t>Excelencia academica-B26-6.png</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Hackaton Final-4</t>
+          <t>Hackaton Final-1</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Hackaton Final-4.png</t>
+          <t>Hackaton Final-1.png</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Hackaton Final-5</t>
+          <t>Hackaton Final-10</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Hackaton Final-5.png</t>
+          <t>Hackaton Final-10.png</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Hackaton Final-6</t>
+          <t>Hackaton Final-11</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Hackaton Final-6.png</t>
+          <t>Hackaton Final-11.png</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Hackaton Final-7</t>
+          <t>Hackaton Final-12</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Hackaton Final-7.png</t>
+          <t>Hackaton Final-12.png</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Hackaton Final-8</t>
+          <t>Hackaton Final-2</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Hackaton Final-8.png</t>
+          <t>Hackaton Final-2.png</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Hackaton Final-9</t>
+          <t>Hackaton Final-3</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Hackaton Final-9.png</t>
+          <t>Hackaton Final-3.png</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Mejores docentes-1</t>
+          <t>Hackaton Final-4</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Mejores docentes-1.png</t>
+          <t>Hackaton Final-4.png</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Mejores docentes-2</t>
+          <t>Hackaton Final-5</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Mejores docentes-2.png</t>
+          <t>Hackaton Final-5.png</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Mejores docentes-3</t>
+          <t>Hackaton Final-6</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Mejores docentes-3.png</t>
+          <t>Hackaton Final-6.png</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-1</t>
+          <t>Hackaton Final-7</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-1.png</t>
+          <t>Hackaton Final-7.png</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-10</t>
+          <t>Hackaton Final-8</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-10.png</t>
+          <t>Hackaton Final-8.png</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-11</t>
+          <t>Hackaton Final-9</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-11.png</t>
+          <t>Hackaton Final-9.png</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-12</t>
+          <t>Mejores docentes-1</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-12.png</t>
+          <t>Mejores docentes-1.png</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-13</t>
+          <t>Mejores docentes-2</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-13.png</t>
+          <t>Mejores docentes-2.png</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-14</t>
+          <t>Mejores docentes-3</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-14.png</t>
+          <t>Mejores docentes-3.png</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-15</t>
+          <t>Mejores promedios-1</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-15.png</t>
+          <t>Mejores promedios-1.png</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-16</t>
+          <t>Mejores promedios-10</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-16.png</t>
+          <t>Mejores promedios-10.png</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-17</t>
+          <t>Mejores promedios-11</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-17.png</t>
+          <t>Mejores promedios-11.png</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-2</t>
+          <t>Mejores promedios-12</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-2.png</t>
+          <t>Mejores promedios-12.png</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-3</t>
+          <t>Mejores promedios-13</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-3.png</t>
+          <t>Mejores promedios-13.png</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-4</t>
+          <t>Mejores promedios-14</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-4.png</t>
+          <t>Mejores promedios-14.png</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-5</t>
+          <t>Mejores promedios-15</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-5.png</t>
+          <t>Mejores promedios-15.png</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-6</t>
+          <t>Mejores promedios-16</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-6.png</t>
+          <t>Mejores promedios-16.png</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-7</t>
+          <t>Mejores promedios-17</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Mejores promedios-7.png</t>
+          <t>Mejores promedios-17.png</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-8</t>
+          <t>Mejores promedios-2</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Mejores promedios-8.png</t>
+          <t>Mejores promedios-2.png</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>12/06/2026 16:44</t>
+          <t>12/06/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1825,43 +1825,253 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
+          <t>Mejores promedios-3</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-3.png</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>A260389.pdf</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>A260389</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>https://indoamericacertificados.github.io/certificados/A260389.pdf</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>12/06/2026 16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-4</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-4.png</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>A260390.pdf</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>A260390</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>https://indoamericacertificados.github.io/certificados/A260390.pdf</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>12/06/2026 16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-5</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-5.png</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>A260402.pdf</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>A260402</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>https://indoamericacertificados.github.io/certificados/A260402.pdf</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>12/06/2026 16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-6</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-6.png</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>A260413.pdf</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>A260413</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>https://indoamericacertificados.github.io/certificados/A260413.pdf</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>12/06/2026 16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-7</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-7.png</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>A260424.pdf</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>A260424</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>https://indoamericacertificados.github.io/certificados/A260424.pdf</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>12/06/2026 16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-8</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-8.png</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>A260435.pdf</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>A260435</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>https://indoamericacertificados.github.io/certificados/A260435.pdf</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>12/06/2026 16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
           <t>Mejores promedios-9</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Mejores promedios-9.png</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>A260389.pdf</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>A260389</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>https://indoamericacertificados.github.io/certificados/A260389.pdf</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>12/06/2026 16:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>A260446.pdf</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>A260446</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>https://indoamericacertificados.github.io/certificados/A260446.pdf</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>12/06/2026 16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B40" s="8" t="n">
-        <v>38</v>
+      <c r="B46" s="8" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1904,6 +2114,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
